--- a/static/roster_template.xlsx
+++ b/static/roster_template.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Roster" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Route Assignments" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,32 +25,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="000F1A2E"/>
-        <bgColor rgb="000F1A2E"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -58,32 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D0D0D0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,299 +413,110 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Driver Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Vehicle Code</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Vehicle Plate</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Route</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Staging</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Pad</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Wave Time</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Route code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>DSP</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Transporter Id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Driver name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Route progress</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery service type</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Route duration</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>All stops</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Stops completed</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Not started stops</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Steven Parker</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>+447700100001</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>LMR11</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>DZ66RY</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>CX305</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>STG.H.10</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>11:45 AM</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>David Chen</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>+447700100002</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>LMR12</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>AB12CD</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>CX210</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>STG.A.05</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>10:30 AM</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Sarah Mitchell</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>+447700100003</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>LMR15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>EF34GH</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>CX118</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>STG.C.02</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>09:15 AM</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>James Wilson</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>+447700100004</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>LMR18</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>IJ56KL</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>CX422</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>STG.D.08</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12:00 PM</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Maria Garcia</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>+447700100005</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>LMR21</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>MN78OP</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>CX509</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>STG.F.12</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>01:15 PM</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>03/07/2026</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RC001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>DSP_A</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRANS001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>John Doe</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8 hours</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
